--- a/diseases/d020/2000-2004.xlsx
+++ b/diseases/d020/2000-2004.xlsx
@@ -2689,9 +2689,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -2985,9 +2982,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3281,9 +3275,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3577,9 +3568,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3873,9 +3861,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4169,9 +4154,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4465,9 +4447,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4761,9 +4740,6 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -5057,9 +5033,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5353,9 +5326,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5649,9 +5619,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -5945,9 +5912,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6241,9 +6205,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6537,9 +6498,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -6833,9 +6791,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7129,9 +7084,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7425,9 +7377,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -7721,9 +7670,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8017,9 +7963,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8313,9 +8256,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8609,9 +8549,6 @@
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -8905,9 +8842,6 @@
       <c r="O57" t="n">
         <v>4</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.008456816866182533</v>
       </c>
@@ -9201,9 +9135,6 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -9497,9 +9428,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -9793,9 +9721,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10089,9 +10014,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10385,9 +10307,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10681,9 +10600,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -10977,9 +10893,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11421,9 +11334,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -11865,9 +11775,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12309,9 +12216,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -12753,9 +12657,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13049,9 +12950,6 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -13493,9 +13391,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -13789,9 +13684,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -14233,9 +14125,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -14677,9 +14566,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15121,9 +15007,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -15565,9 +15448,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -16009,9 +15889,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16601,9 +16478,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17193,9 +17067,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -17785,9 +17656,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18377,9 +18245,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -18821,9 +18686,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -19413,9 +19275,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -19855,9 +19714,6 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
